--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC446C97-2374-5649-9402-19595947077A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F08A02A-7B6C-CC44-AD7D-EB204E807620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -991,7 +991,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H2" s="3"/>
       <c r="M2" s="7"/>
@@ -1007,7 +1007,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="6">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="H3" s="3"/>
       <c r="M3" s="7"/>
@@ -1023,7 +1023,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="3"/>
       <c r="M4" s="7"/>
@@ -1039,7 +1039,7 @@
         <v>22</v>
       </c>
       <c r="D5" s="6">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="3"/>
       <c r="M5" s="7"/>
@@ -1055,7 +1055,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="6">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="M6" s="4"/>
     </row>
@@ -1070,7 +1070,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H7" s="3"/>
       <c r="M7" s="4"/>
@@ -1086,7 +1086,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="H8" s="3"/>
       <c r="M8" s="4"/>
@@ -1102,7 +1102,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="6">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H9" s="3"/>
       <c r="M9" s="4"/>
@@ -1118,7 +1118,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="6">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H10" s="3"/>
       <c r="M10" s="4"/>
@@ -1134,7 +1134,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H11" s="3"/>
       <c r="M11" s="4"/>
@@ -1150,7 +1150,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="6">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="3"/>
       <c r="M12" s="4"/>
@@ -1166,7 +1166,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H13" s="3"/>
       <c r="M13" s="4"/>
@@ -1182,7 +1182,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H14" s="3"/>
       <c r="M14" s="4"/>
@@ -1198,7 +1198,7 @@
         <v>42</v>
       </c>
       <c r="D15" s="6">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="3"/>
       <c r="M15" s="4"/>
@@ -1214,7 +1214,7 @@
         <v>44</v>
       </c>
       <c r="D16" s="6">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="H16" s="3"/>
       <c r="M16" s="4"/>
@@ -1230,7 +1230,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="6">
-        <v>0.69</v>
+        <v>0.76</v>
       </c>
       <c r="M17" s="4"/>
     </row>
@@ -1245,7 +1245,7 @@
         <v>48</v>
       </c>
       <c r="D18" s="6">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H18" s="3"/>
       <c r="M18" s="4"/>
@@ -1261,7 +1261,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="6">
-        <v>0.87</v>
+        <v>0.94</v>
       </c>
       <c r="M19" s="4"/>
     </row>
@@ -1276,7 +1276,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H20" s="3"/>
       <c r="M20" s="4"/>
@@ -1292,7 +1292,7 @@
         <v>54</v>
       </c>
       <c r="D21" s="6">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="3"/>
       <c r="M21" s="4"/>
@@ -1308,7 +1308,7 @@
         <v>56</v>
       </c>
       <c r="D22" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M22" s="4"/>
     </row>
@@ -1323,7 +1323,7 @@
         <v>58</v>
       </c>
       <c r="D23" s="6">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="H23" s="3"/>
       <c r="M23" s="4"/>
@@ -1339,7 +1339,7 @@
         <v>60</v>
       </c>
       <c r="D24" s="6">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="H24" s="3"/>
       <c r="M24" s="4"/>
@@ -1355,7 +1355,7 @@
         <v>62</v>
       </c>
       <c r="D25" s="6">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="H25" s="3"/>
       <c r="M25" s="4"/>
@@ -1371,7 +1371,7 @@
         <v>64</v>
       </c>
       <c r="D26" s="6">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="M26" s="4"/>
     </row>
@@ -1402,7 +1402,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="6">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="H28" s="3"/>
       <c r="M28" s="4"/>
@@ -1418,7 +1418,7 @@
         <v>70</v>
       </c>
       <c r="D29" s="6">
-        <v>0.87</v>
+        <v>0.94</v>
       </c>
       <c r="M29" s="4"/>
     </row>
@@ -1433,7 +1433,7 @@
         <v>72</v>
       </c>
       <c r="D30" s="6">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="H30" s="3"/>
       <c r="M30" s="4"/>
@@ -1449,7 +1449,7 @@
         <v>74</v>
       </c>
       <c r="D31" s="6">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="H31" s="3"/>
       <c r="M31" s="4"/>
@@ -1465,7 +1465,7 @@
         <v>76</v>
       </c>
       <c r="D32" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M32" s="4"/>
     </row>
@@ -1480,7 +1480,7 @@
         <v>78</v>
       </c>
       <c r="D33" s="6">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="H33" s="3"/>
       <c r="M33" s="8"/>
@@ -1496,7 +1496,7 @@
         <v>80</v>
       </c>
       <c r="D34" s="6">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H34" s="3"/>
       <c r="M34" s="4"/>
@@ -1512,7 +1512,7 @@
         <v>82</v>
       </c>
       <c r="D35" s="6">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="M35" s="4"/>
     </row>
@@ -1527,7 +1527,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H36" s="3"/>
       <c r="M36" s="4"/>
@@ -1543,7 +1543,7 @@
         <v>86</v>
       </c>
       <c r="D37" s="6">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M37" s="4"/>
     </row>
@@ -1558,7 +1558,7 @@
         <v>88</v>
       </c>
       <c r="D38" s="6">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H38" s="3"/>
       <c r="M38" s="4"/>
@@ -1574,7 +1574,7 @@
         <v>90</v>
       </c>
       <c r="D39" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H39" s="3"/>
       <c r="M39" s="4"/>
@@ -1590,7 +1590,7 @@
         <v>91</v>
       </c>
       <c r="D40" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H40" s="3"/>
       <c r="M40" s="4"/>
@@ -1606,7 +1606,7 @@
         <v>93</v>
       </c>
       <c r="D41" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H41" s="3"/>
       <c r="M41" s="4"/>
@@ -1622,7 +1622,7 @@
         <v>95</v>
       </c>
       <c r="D42" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="M42" s="4"/>
     </row>
@@ -1637,7 +1637,7 @@
         <v>97</v>
       </c>
       <c r="D43" s="6">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H43" s="3"/>
       <c r="M43" s="8"/>
@@ -1653,7 +1653,7 @@
         <v>99</v>
       </c>
       <c r="D44" s="6">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="H44" s="3"/>
       <c r="M44" s="8"/>
@@ -1669,7 +1669,7 @@
         <v>101</v>
       </c>
       <c r="D45" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H45" s="3"/>
       <c r="M45" s="4"/>
@@ -1685,7 +1685,7 @@
         <v>103</v>
       </c>
       <c r="D46" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H46" s="3"/>
       <c r="M46" s="4"/>
@@ -1701,7 +1701,7 @@
         <v>105</v>
       </c>
       <c r="D47" s="6">
-        <v>0.69</v>
+        <v>0.73</v>
       </c>
       <c r="H47" s="3"/>
       <c r="M47" s="4"/>
@@ -1717,7 +1717,7 @@
         <v>108</v>
       </c>
       <c r="D48" s="6">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M48" s="4"/>
     </row>
@@ -1732,7 +1732,7 @@
         <v>110</v>
       </c>
       <c r="D49" s="6">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="M49" s="4"/>
     </row>
@@ -1747,7 +1747,7 @@
         <v>112</v>
       </c>
       <c r="D50" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="M50" s="4"/>
     </row>
@@ -1762,7 +1762,7 @@
         <v>114</v>
       </c>
       <c r="D51" s="6">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H51" s="3"/>
       <c r="M51" s="4"/>
@@ -1778,7 +1778,7 @@
         <v>116</v>
       </c>
       <c r="D52" s="6">
-        <v>0.69</v>
+        <v>0.76</v>
       </c>
       <c r="H52" s="3"/>
       <c r="M52" s="4"/>
@@ -1794,7 +1794,7 @@
         <v>118</v>
       </c>
       <c r="D53" s="6">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="H53" s="3"/>
       <c r="M53" s="4"/>
@@ -1810,7 +1810,7 @@
         <v>120</v>
       </c>
       <c r="D54" s="6">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="M54" s="4"/>
     </row>
@@ -1825,7 +1825,7 @@
         <v>122</v>
       </c>
       <c r="D55" s="6">
-        <v>0.62</v>
+        <v>0.69</v>
       </c>
       <c r="H55" s="3"/>
       <c r="M55" s="4"/>
@@ -1841,7 +1841,7 @@
         <v>124</v>
       </c>
       <c r="D56" s="6">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="H56" s="3"/>
       <c r="M56" s="4"/>
@@ -1857,7 +1857,7 @@
         <v>126</v>
       </c>
       <c r="D57" s="6">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="M57" s="4"/>
     </row>
@@ -1872,7 +1872,7 @@
         <v>128</v>
       </c>
       <c r="D58" s="6">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="H58" s="3"/>
       <c r="M58" s="4"/>
@@ -1888,7 +1888,7 @@
         <v>130</v>
       </c>
       <c r="D59" s="6">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="H59" s="3"/>
       <c r="M59" s="4"/>
@@ -1904,7 +1904,7 @@
         <v>132</v>
       </c>
       <c r="D60" s="6">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H60" s="3"/>
       <c r="M60" s="4"/>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F08A02A-7B6C-CC44-AD7D-EB204E807620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F707877F-1877-7442-911C-F3E01DF993BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="7980" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -993,6 +993,9 @@
       <c r="D2" s="6">
         <v>0.89</v>
       </c>
+      <c r="G2">
+        <v>0.33</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="M2" s="7"/>
     </row>
@@ -1009,6 +1012,9 @@
       <c r="D3" s="6">
         <v>0.92</v>
       </c>
+      <c r="G3">
+        <v>0.64</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="M3" s="7"/>
     </row>
@@ -1025,6 +1031,9 @@
       <c r="D4" s="6">
         <v>0.85</v>
       </c>
+      <c r="G4">
+        <v>0.34</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="M4" s="7"/>
     </row>
@@ -1041,6 +1050,9 @@
       <c r="D5" s="6">
         <v>0.82</v>
       </c>
+      <c r="G5">
+        <v>0.61</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="M5" s="7"/>
     </row>
@@ -1057,6 +1069,9 @@
       <c r="D6" s="6">
         <v>0.8</v>
       </c>
+      <c r="G6">
+        <v>0.31</v>
+      </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
@@ -1072,6 +1087,9 @@
       <c r="D7" s="6">
         <v>0.86</v>
       </c>
+      <c r="G7">
+        <v>0.37</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="M7" s="4"/>
     </row>
@@ -1088,6 +1106,9 @@
       <c r="D8" s="6">
         <v>0.92</v>
       </c>
+      <c r="G8">
+        <v>0.43</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="M8" s="4"/>
     </row>
@@ -1104,6 +1125,9 @@
       <c r="D9" s="6">
         <v>0.97</v>
       </c>
+      <c r="G9">
+        <v>0.49</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="M9" s="4"/>
     </row>
@@ -1120,6 +1144,9 @@
       <c r="D10" s="6">
         <v>0.7</v>
       </c>
+      <c r="G10">
+        <v>0.69</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="M10" s="4"/>
     </row>
@@ -1136,6 +1163,9 @@
       <c r="D11" s="6">
         <v>0.86</v>
       </c>
+      <c r="G11">
+        <v>0.45</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="M11" s="4"/>
     </row>
@@ -1152,6 +1182,9 @@
       <c r="D12" s="6">
         <v>0.97</v>
       </c>
+      <c r="G12">
+        <v>0.61</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="M12" s="4"/>
     </row>
@@ -1168,6 +1201,9 @@
       <c r="D13" s="6">
         <v>0.86</v>
       </c>
+      <c r="G13">
+        <v>0.22</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="M13" s="4"/>
     </row>
@@ -1184,6 +1220,9 @@
       <c r="D14" s="6">
         <v>0.7</v>
       </c>
+      <c r="G14">
+        <v>0.82</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="M14" s="4"/>
     </row>
@@ -1200,6 +1239,9 @@
       <c r="D15" s="6">
         <v>0.75</v>
       </c>
+      <c r="G15">
+        <v>0.36</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="M15" s="4"/>
     </row>
@@ -1216,6 +1258,9 @@
       <c r="D16" s="6">
         <v>0.92</v>
       </c>
+      <c r="G16">
+        <v>0.4</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="M16" s="4"/>
     </row>
@@ -1232,6 +1277,9 @@
       <c r="D17" s="6">
         <v>0.76</v>
       </c>
+      <c r="G17">
+        <v>0.33</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
@@ -1247,6 +1295,9 @@
       <c r="D18" s="6">
         <v>0.87</v>
       </c>
+      <c r="G18">
+        <v>0.49</v>
+      </c>
       <c r="H18" s="3"/>
       <c r="M18" s="4"/>
     </row>
@@ -1263,6 +1314,9 @@
       <c r="D19" s="6">
         <v>0.94</v>
       </c>
+      <c r="G19">
+        <v>0.34</v>
+      </c>
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13">
@@ -1278,6 +1332,9 @@
       <c r="D20" s="6">
         <v>0.93</v>
       </c>
+      <c r="G20">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="M20" s="4"/>
     </row>
@@ -1294,6 +1351,9 @@
       <c r="D21" s="6">
         <v>0.7</v>
       </c>
+      <c r="G21">
+        <v>0.46</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="M21" s="4"/>
     </row>
@@ -1310,6 +1370,9 @@
       <c r="D22" s="6">
         <v>0.85</v>
       </c>
+      <c r="G22">
+        <v>0.6</v>
+      </c>
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13">
@@ -1325,6 +1388,9 @@
       <c r="D23" s="6">
         <v>0.73</v>
       </c>
+      <c r="G23">
+        <v>0.43</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="M23" s="4"/>
     </row>
@@ -1341,6 +1407,9 @@
       <c r="D24" s="6">
         <v>0.8</v>
       </c>
+      <c r="G24">
+        <v>0.51</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="M24" s="4"/>
     </row>
@@ -1357,6 +1426,9 @@
       <c r="D25" s="6">
         <v>0.9</v>
       </c>
+      <c r="G25">
+        <v>0.6</v>
+      </c>
       <c r="H25" s="3"/>
       <c r="M25" s="4"/>
     </row>
@@ -1373,6 +1445,9 @@
       <c r="D26" s="6">
         <v>0.83</v>
       </c>
+      <c r="G26">
+        <v>0.61</v>
+      </c>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="1:13">
@@ -1388,6 +1463,9 @@
       <c r="D27" s="6">
         <v>0.63</v>
       </c>
+      <c r="G27">
+        <v>0.33</v>
+      </c>
       <c r="H27" s="3"/>
       <c r="M27" s="8"/>
     </row>
@@ -1404,6 +1482,9 @@
       <c r="D28" s="6">
         <v>0.9</v>
       </c>
+      <c r="G28">
+        <v>0.84</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="M28" s="4"/>
     </row>
@@ -1420,6 +1501,9 @@
       <c r="D29" s="6">
         <v>0.94</v>
       </c>
+      <c r="G29">
+        <v>0.6</v>
+      </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="1:13">
@@ -1435,6 +1519,9 @@
       <c r="D30" s="6">
         <v>0.93</v>
       </c>
+      <c r="G30">
+        <v>0.46</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="M30" s="4"/>
     </row>
@@ -1451,6 +1538,9 @@
       <c r="D31" s="6">
         <v>0.86</v>
       </c>
+      <c r="G31">
+        <v>0.69</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="M31" s="4"/>
     </row>
@@ -1467,6 +1557,9 @@
       <c r="D32" s="6">
         <v>0.86</v>
       </c>
+      <c r="G32">
+        <v>0.84</v>
+      </c>
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="1:13">
@@ -1482,6 +1575,9 @@
       <c r="D33" s="6">
         <v>0.82</v>
       </c>
+      <c r="G33">
+        <v>0.45</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="M33" s="8"/>
     </row>
@@ -1498,6 +1594,9 @@
       <c r="D34" s="6">
         <v>0.96</v>
       </c>
+      <c r="G34">
+        <v>0.66</v>
+      </c>
       <c r="H34" s="3"/>
       <c r="M34" s="4"/>
     </row>
@@ -1514,6 +1613,9 @@
       <c r="D35" s="6">
         <v>0.83</v>
       </c>
+      <c r="G35">
+        <v>0.25</v>
+      </c>
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13">
@@ -1529,6 +1631,9 @@
       <c r="D36" s="6">
         <v>0.89</v>
       </c>
+      <c r="G36">
+        <v>0.24</v>
+      </c>
       <c r="H36" s="3"/>
       <c r="M36" s="4"/>
     </row>
@@ -1545,6 +1650,9 @@
       <c r="D37" s="6">
         <v>0.82</v>
       </c>
+      <c r="G37">
+        <v>0.42</v>
+      </c>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
@@ -1560,6 +1668,9 @@
       <c r="D38" s="6">
         <v>0.83</v>
       </c>
+      <c r="G38">
+        <v>0.61</v>
+      </c>
       <c r="H38" s="3"/>
       <c r="M38" s="4"/>
     </row>
@@ -1576,6 +1687,9 @@
       <c r="D39" s="6">
         <v>0.85</v>
       </c>
+      <c r="G39">
+        <v>0.45</v>
+      </c>
       <c r="H39" s="3"/>
       <c r="M39" s="4"/>
     </row>
@@ -1592,6 +1706,9 @@
       <c r="D40" s="6">
         <v>0.89</v>
       </c>
+      <c r="G40">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H40" s="3"/>
       <c r="M40" s="4"/>
     </row>
@@ -1608,6 +1725,9 @@
       <c r="D41" s="6">
         <v>0.86</v>
       </c>
+      <c r="G41">
+        <v>0.22</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="M41" s="4"/>
     </row>
@@ -1624,6 +1744,9 @@
       <c r="D42" s="6">
         <v>0.89</v>
       </c>
+      <c r="G42">
+        <v>0.43</v>
+      </c>
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13">
@@ -1639,6 +1762,9 @@
       <c r="D43" s="6">
         <v>0.82</v>
       </c>
+      <c r="G43">
+        <v>0.6</v>
+      </c>
       <c r="H43" s="3"/>
       <c r="M43" s="8"/>
     </row>
@@ -1655,6 +1781,9 @@
       <c r="D44" s="6">
         <v>0.8</v>
       </c>
+      <c r="G44">
+        <v>0.63</v>
+      </c>
       <c r="H44" s="3"/>
       <c r="M44" s="8"/>
     </row>
@@ -1671,6 +1800,9 @@
       <c r="D45" s="6">
         <v>0.85</v>
       </c>
+      <c r="G45">
+        <v>0.63</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="M45" s="4"/>
     </row>
@@ -1687,6 +1819,9 @@
       <c r="D46" s="6">
         <v>0.89</v>
       </c>
+      <c r="G46">
+        <v>0.46</v>
+      </c>
       <c r="H46" s="3"/>
       <c r="M46" s="4"/>
     </row>
@@ -1703,6 +1838,9 @@
       <c r="D47" s="6">
         <v>0.73</v>
       </c>
+      <c r="G47">
+        <v>0.45</v>
+      </c>
       <c r="H47" s="3"/>
       <c r="M47" s="4"/>
     </row>
@@ -1719,6 +1857,9 @@
       <c r="D48" s="6">
         <v>0.9</v>
       </c>
+      <c r="G48">
+        <v>0.49</v>
+      </c>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
@@ -1734,6 +1875,9 @@
       <c r="D49" s="6">
         <v>0.83</v>
       </c>
+      <c r="G49">
+        <v>0.46</v>
+      </c>
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13">
@@ -1749,6 +1893,9 @@
       <c r="D50" s="6">
         <v>0.85</v>
       </c>
+      <c r="G50">
+        <v>0.43</v>
+      </c>
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13">
@@ -1764,6 +1911,9 @@
       <c r="D51" s="6">
         <v>0.7</v>
       </c>
+      <c r="G51">
+        <v>0.34</v>
+      </c>
       <c r="H51" s="3"/>
       <c r="M51" s="4"/>
     </row>
@@ -1780,6 +1930,9 @@
       <c r="D52" s="6">
         <v>0.76</v>
       </c>
+      <c r="G52">
+        <v>0.61</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="M52" s="4"/>
     </row>
@@ -1796,6 +1949,9 @@
       <c r="D53" s="6">
         <v>0.9</v>
       </c>
+      <c r="G53">
+        <v>0.51</v>
+      </c>
       <c r="H53" s="3"/>
       <c r="M53" s="4"/>
     </row>
@@ -1812,6 +1968,9 @@
       <c r="D54" s="6">
         <v>0.75</v>
       </c>
+      <c r="G54">
+        <v>0.49</v>
+      </c>
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13">
@@ -1827,6 +1986,9 @@
       <c r="D55" s="6">
         <v>0.69</v>
       </c>
+      <c r="G55">
+        <v>0.45</v>
+      </c>
       <c r="H55" s="3"/>
       <c r="M55" s="4"/>
     </row>
@@ -1843,6 +2005,9 @@
       <c r="D56" s="6">
         <v>0.18</v>
       </c>
+      <c r="G56">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="H56" s="3"/>
       <c r="M56" s="4"/>
     </row>
@@ -1859,6 +2024,9 @@
       <c r="D57" s="6">
         <v>0.72</v>
       </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13">
@@ -1874,6 +2042,9 @@
       <c r="D58" s="6">
         <v>0.77</v>
       </c>
+      <c r="G58">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H58" s="3"/>
       <c r="M58" s="4"/>
     </row>
@@ -1890,6 +2061,9 @@
       <c r="D59" s="6">
         <v>0.92</v>
       </c>
+      <c r="G59">
+        <v>0.52</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="M59" s="4"/>
     </row>
@@ -1905,6 +2079,9 @@
       </c>
       <c r="D60" s="6">
         <v>0.66</v>
+      </c>
+      <c r="G60">
+        <v>0.43</v>
       </c>
       <c r="H60" s="3"/>
       <c r="M60" s="4"/>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F707877F-1877-7442-911C-F3E01DF993BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6EFD3D-8075-8F4E-BDA6-F838BFB9DFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="3180" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1054,6 +1054,9 @@
         <v>0.61</v>
       </c>
       <c r="H5" s="3"/>
+      <c r="J5">
+        <v>0.79</v>
+      </c>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
@@ -1110,6 +1113,9 @@
         <v>0.43</v>
       </c>
       <c r="H8" s="3"/>
+      <c r="J8">
+        <v>0.79</v>
+      </c>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13">
@@ -1317,6 +1323,9 @@
       <c r="G19">
         <v>0.34</v>
       </c>
+      <c r="J19">
+        <v>0.79</v>
+      </c>
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13">
@@ -1373,6 +1382,9 @@
       <c r="G22">
         <v>0.6</v>
       </c>
+      <c r="J22">
+        <v>0.79</v>
+      </c>
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13">
@@ -1411,6 +1423,9 @@
         <v>0.51</v>
       </c>
       <c r="H24" s="3"/>
+      <c r="J24">
+        <v>0.79</v>
+      </c>
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13">
@@ -1467,6 +1482,9 @@
         <v>0.33</v>
       </c>
       <c r="H27" s="3"/>
+      <c r="J27">
+        <v>0.79</v>
+      </c>
       <c r="M27" s="8"/>
     </row>
     <row r="28" spans="1:13">
@@ -1504,6 +1522,9 @@
       <c r="G29">
         <v>0.6</v>
       </c>
+      <c r="J29">
+        <v>0.79</v>
+      </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="1:13">
@@ -1523,6 +1544,9 @@
         <v>0.46</v>
       </c>
       <c r="H30" s="3"/>
+      <c r="J30">
+        <v>0.79</v>
+      </c>
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13">
@@ -1804,6 +1828,9 @@
         <v>0.63</v>
       </c>
       <c r="H45" s="3"/>
+      <c r="J45">
+        <v>0.79</v>
+      </c>
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="1:13">
@@ -1823,6 +1850,9 @@
         <v>0.46</v>
       </c>
       <c r="H46" s="3"/>
+      <c r="J46">
+        <v>0.79</v>
+      </c>
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="1:13">

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6EFD3D-8075-8F4E-BDA6-F838BFB9DFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971A391B-450E-F543-BE64-5E32F910A7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3180" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -997,6 +997,9 @@
         <v>0.33</v>
       </c>
       <c r="H2" s="3"/>
+      <c r="J2">
+        <v>0.6</v>
+      </c>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13">
@@ -1016,6 +1019,9 @@
         <v>0.64</v>
       </c>
       <c r="H3" s="3"/>
+      <c r="J3">
+        <v>0.25</v>
+      </c>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13">
@@ -1094,6 +1100,9 @@
         <v>0.37</v>
       </c>
       <c r="H7" s="3"/>
+      <c r="J7">
+        <v>0.6</v>
+      </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13">
@@ -1135,6 +1144,9 @@
         <v>0.49</v>
       </c>
       <c r="H9" s="3"/>
+      <c r="J9">
+        <v>0.25</v>
+      </c>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13">
@@ -1268,6 +1280,9 @@
         <v>0.4</v>
       </c>
       <c r="H16" s="3"/>
+      <c r="J16">
+        <v>0.25</v>
+      </c>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13">
@@ -1286,6 +1301,9 @@
       <c r="G17">
         <v>0.33</v>
       </c>
+      <c r="J17">
+        <v>0.6</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
@@ -1305,6 +1323,9 @@
         <v>0.49</v>
       </c>
       <c r="H18" s="3"/>
+      <c r="J18">
+        <v>0.25</v>
+      </c>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
@@ -1364,6 +1385,9 @@
         <v>0.46</v>
       </c>
       <c r="H21" s="3"/>
+      <c r="J21">
+        <v>0.6</v>
+      </c>
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="1:13">
@@ -1622,6 +1646,9 @@
         <v>0.66</v>
       </c>
       <c r="H34" s="3"/>
+      <c r="J34">
+        <v>0.71</v>
+      </c>
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13">
@@ -1659,6 +1686,9 @@
         <v>0.24</v>
       </c>
       <c r="H36" s="3"/>
+      <c r="J36">
+        <v>0.71</v>
+      </c>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
@@ -1734,6 +1764,9 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H40" s="3"/>
+      <c r="J40">
+        <v>0.6</v>
+      </c>
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="1:13">
@@ -1771,6 +1804,9 @@
       <c r="G42">
         <v>0.43</v>
       </c>
+      <c r="J42">
+        <v>0.71</v>
+      </c>
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13">
@@ -1809,6 +1845,9 @@
         <v>0.63</v>
       </c>
       <c r="H44" s="3"/>
+      <c r="J44">
+        <v>0.71</v>
+      </c>
       <c r="M44" s="8"/>
     </row>
     <row r="45" spans="1:13">

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971A391B-450E-F543-BE64-5E32F910A7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE02225B-6FBF-1B4E-AE5C-9E1CE1B87D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3180" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1041,6 +1041,9 @@
         <v>0.34</v>
       </c>
       <c r="H4" s="3"/>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13">
@@ -1081,6 +1084,9 @@
       <c r="G6">
         <v>0.31</v>
       </c>
+      <c r="J6">
+        <v>0.77</v>
+      </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
@@ -1166,6 +1172,9 @@
         <v>0.69</v>
       </c>
       <c r="H10" s="3"/>
+      <c r="J10">
+        <v>0</v>
+      </c>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13">
@@ -1185,6 +1194,9 @@
         <v>0.45</v>
       </c>
       <c r="H11" s="3"/>
+      <c r="J11">
+        <v>0.77</v>
+      </c>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13">
@@ -1204,6 +1216,9 @@
         <v>0.61</v>
       </c>
       <c r="H12" s="3"/>
+      <c r="J12">
+        <v>0</v>
+      </c>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13">
@@ -1223,6 +1238,9 @@
         <v>0.22</v>
       </c>
       <c r="H13" s="3"/>
+      <c r="J13">
+        <v>0</v>
+      </c>
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13">
@@ -1242,6 +1260,9 @@
         <v>0.82</v>
       </c>
       <c r="H14" s="3"/>
+      <c r="J14">
+        <v>0</v>
+      </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13">
@@ -1261,6 +1282,9 @@
         <v>0.36</v>
       </c>
       <c r="H15" s="3"/>
+      <c r="J15">
+        <v>0</v>
+      </c>
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13">
@@ -1366,6 +1390,9 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H20" s="3"/>
+      <c r="J20">
+        <v>0.79</v>
+      </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13">
@@ -1428,6 +1455,9 @@
         <v>0.43</v>
       </c>
       <c r="H23" s="3"/>
+      <c r="J23">
+        <v>0.79</v>
+      </c>
       <c r="M23" s="4"/>
     </row>
     <row r="24" spans="1:13">
@@ -1469,6 +1499,9 @@
         <v>0.6</v>
       </c>
       <c r="H25" s="3"/>
+      <c r="J25">
+        <v>0.77</v>
+      </c>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="1:13">
@@ -1487,6 +1520,9 @@
       <c r="G26">
         <v>0.61</v>
       </c>
+      <c r="J26">
+        <v>0.79</v>
+      </c>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="1:13">
@@ -1528,6 +1564,9 @@
         <v>0.84</v>
       </c>
       <c r="H28" s="3"/>
+      <c r="J28">
+        <v>0.74</v>
+      </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13">
@@ -1590,6 +1629,9 @@
         <v>0.69</v>
       </c>
       <c r="H31" s="3"/>
+      <c r="J31">
+        <v>0.77</v>
+      </c>
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="1:13">
@@ -1608,6 +1650,9 @@
       <c r="G32">
         <v>0.84</v>
       </c>
+      <c r="J32">
+        <v>0.74</v>
+      </c>
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="1:13">
@@ -1627,6 +1672,9 @@
         <v>0.45</v>
       </c>
       <c r="H33" s="3"/>
+      <c r="J33">
+        <v>0.77</v>
+      </c>
       <c r="M33" s="8"/>
     </row>
     <row r="34" spans="1:13">
@@ -1667,6 +1715,9 @@
       <c r="G35">
         <v>0.25</v>
       </c>
+      <c r="J35">
+        <v>0.74</v>
+      </c>
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13">
@@ -1707,6 +1758,9 @@
       <c r="G37">
         <v>0.42</v>
       </c>
+      <c r="J37">
+        <v>0.79</v>
+      </c>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
@@ -1726,6 +1780,9 @@
         <v>0.61</v>
       </c>
       <c r="H38" s="3"/>
+      <c r="J38">
+        <v>0.77</v>
+      </c>
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13">
@@ -1745,6 +1802,9 @@
         <v>0.45</v>
       </c>
       <c r="H39" s="3"/>
+      <c r="J39">
+        <v>0.77</v>
+      </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
@@ -1786,6 +1846,9 @@
         <v>0.22</v>
       </c>
       <c r="H41" s="3"/>
+      <c r="J41">
+        <v>0.77</v>
+      </c>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
@@ -1826,6 +1889,9 @@
         <v>0.6</v>
       </c>
       <c r="H43" s="3"/>
+      <c r="J43">
+        <v>0.77</v>
+      </c>
       <c r="M43" s="8"/>
     </row>
     <row r="44" spans="1:13">
@@ -1911,6 +1977,9 @@
         <v>0.45</v>
       </c>
       <c r="H47" s="3"/>
+      <c r="J47">
+        <v>0.74</v>
+      </c>
       <c r="M47" s="4"/>
     </row>
     <row r="48" spans="1:13">
@@ -1929,6 +1998,9 @@
       <c r="G48">
         <v>0.49</v>
       </c>
+      <c r="J48">
+        <v>0.73</v>
+      </c>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
@@ -1947,6 +2019,9 @@
       <c r="G49">
         <v>0.46</v>
       </c>
+      <c r="J49">
+        <v>0.77</v>
+      </c>
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13">
@@ -1965,6 +2040,9 @@
       <c r="G50">
         <v>0.43</v>
       </c>
+      <c r="J50">
+        <v>0.73</v>
+      </c>
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13">
@@ -1984,6 +2062,9 @@
         <v>0.34</v>
       </c>
       <c r="H51" s="3"/>
+      <c r="J51">
+        <v>0.74</v>
+      </c>
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13">
@@ -2003,6 +2084,9 @@
         <v>0.61</v>
       </c>
       <c r="H52" s="3"/>
+      <c r="J52">
+        <v>0.74</v>
+      </c>
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="1:13">
@@ -2022,6 +2106,9 @@
         <v>0.51</v>
       </c>
       <c r="H53" s="3"/>
+      <c r="J53">
+        <v>0.77</v>
+      </c>
       <c r="M53" s="4"/>
     </row>
     <row r="54" spans="1:13">
@@ -2040,6 +2127,9 @@
       <c r="G54">
         <v>0.49</v>
       </c>
+      <c r="J54">
+        <v>0.73</v>
+      </c>
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13">
@@ -2059,6 +2149,9 @@
         <v>0.45</v>
       </c>
       <c r="H55" s="3"/>
+      <c r="J55">
+        <v>0.74</v>
+      </c>
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13">
@@ -2078,6 +2171,9 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="H56" s="3"/>
+      <c r="J56">
+        <v>0.73</v>
+      </c>
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13">
@@ -2096,6 +2192,9 @@
       <c r="G57">
         <v>0</v>
       </c>
+      <c r="J57">
+        <v>0.73</v>
+      </c>
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13">
@@ -2115,6 +2214,9 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H58" s="3"/>
+      <c r="J58">
+        <v>0.73</v>
+      </c>
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13">
@@ -2134,6 +2236,9 @@
         <v>0.52</v>
       </c>
       <c r="H59" s="3"/>
+      <c r="J59">
+        <v>0.77</v>
+      </c>
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="1:13">
@@ -2153,6 +2258,9 @@
         <v>0.43</v>
       </c>
       <c r="H60" s="3"/>
+      <c r="J60">
+        <v>0.73</v>
+      </c>
       <c r="M60" s="4"/>
     </row>
     <row r="61" spans="1:13">
